--- a/FOA Singles/Mattress-Single.xlsx
+++ b/FOA Singles/Mattress-Single.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -787,15 +787,15 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AFTON 12" Euro Box Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 84"L X 72"W X 12"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 90 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AFTON 12" Euro Box Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 12"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 90 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
@@ -923,15 +923,15 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with AFTON 12" Euro Box Pocket Coil, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 80"L X 76"W X 12"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 90 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with AFTON 12" Euro Box Pocket Coil, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 90 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -1059,15 +1059,15 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AFTON 12" Euro Box Pocket Coil offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 75"L X 54"W X 12"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AFTON 12" Euro Box Pocket Coil offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -1195,15 +1195,15 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AFTON 12" Euro Box Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 80"L X 60"W X 12"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AFTON 12" Euro Box Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Designer Stretch Fabric 5 Layer Tack And Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ALEKSA 11" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.
-Product Dimensions: 84"L X 72"W X 11"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Color: White or Gray
-Weight: 85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ALEKSA 11" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 11"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1462,14 +1462,14 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALEKSA 11" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.
-Product Dimensions: 80"L X 76"W X 11"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Color: White or Gray
-Weight: 85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALEKSA 11" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 11"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -1593,14 +1593,14 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALEKSA 11" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.
-Product Dimensions: 75"L X 54"W X 11"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Color: White or Gray
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALEKSA 11" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 11"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -1724,14 +1724,14 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ALEKSA 11" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.
-Product Dimensions: 80"L X 60"W X 11"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Color: White or Gray
-Weight: 65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ALEKSA 11" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 11"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -1855,16 +1855,16 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 10" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 76"W X 80"D X 10"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 75.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 10" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 10"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 75.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -1992,16 +1992,16 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 10" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"D X 10"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 52.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 10" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 52.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -2129,16 +2129,16 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 10" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"W X 80"D X 10"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 61.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 10" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 61.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -2266,16 +2266,16 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 10" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 10"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 39.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 10" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 10"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 39.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -2403,15 +2403,15 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 10" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 38"W X 80"D X 10"H
-Size: Twin XL
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 10" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 38"W X 80"D X 10"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -2537,16 +2537,16 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 12" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 76"W X 80"D X 12"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 84.39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 12" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 84.39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
@@ -2674,16 +2674,16 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 12"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 59.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 59.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -2811,16 +2811,16 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 12" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 70.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 12" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -2948,16 +2948,16 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 12" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 39"W X 75"D X 12"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 44.66 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 12" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 12"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 44.66 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -3085,15 +3085,15 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 38"W X 80"D X 12"H
-Size: Twin XL
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 38"W X 80"D X 12"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -3219,16 +3219,16 @@
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 6" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"D X 6"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 34.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 6" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 6"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 34.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" s="16" t="inlineStr">
@@ -3356,16 +3356,16 @@
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 6" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"W X 80"D X 6"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 41.58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 6" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 6"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 41.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" s="16" t="inlineStr">
@@ -3493,16 +3493,16 @@
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 6" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 6"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 25.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 6" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 6"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 25.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" s="16" t="inlineStr">
@@ -3630,15 +3630,15 @@
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 6" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 38"W X 80"D X 6"H
-Size: Twin XL
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 6" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 38"W X 80"D X 6"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="16" t="inlineStr">
@@ -3764,16 +3764,16 @@
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 8" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 72"W X 84"D X 8"H
-Size: California King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 8" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 72"W X 84"D X 8"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="18" t="inlineStr">
@@ -3901,16 +3901,16 @@
       </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 8" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 76"W X 80"D X 8"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 63.03 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 8" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 8"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 63.03 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
@@ -4038,16 +4038,16 @@
       </c>
       <c r="G26" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 8" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"D X 8"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 42.79 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 8" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 42.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" s="18" t="inlineStr">
@@ -4175,16 +4175,16 @@
       </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 8" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"W X 80"D X 8"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 8" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Top and Side Cover: 100% Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
@@ -4312,16 +4312,16 @@
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ARTEMISIA 8" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 8"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White
-Weight: 31.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ARTEMISIA 8" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Top and Side Cover: 100% Polyester construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 31.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" s="18" t="inlineStr">
@@ -4449,15 +4449,15 @@
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMISIA 8" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 39"W X 80"D X 8"H
-Size: TXL
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Top and Side Cover: 100% Polyester.
-Color: White</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMISIA 8" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Top and Side Cover: 100% Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 39"W X 80"D X 8"H&lt;br&gt;
+Size: TXL&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Top and Side Cover: 100% Polyester.&lt;br&gt;
+Color: White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
@@ -4575,15 +4575,15 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE 11" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 84"L X 72"W X 11"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 95 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE 11" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 11"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 95 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -4711,15 +4711,15 @@
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE 11" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 80"L X 76"W X 11"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 95 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE 11" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 11"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 95 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -4847,15 +4847,15 @@
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with BIRD OF PARADISE 11" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White tones.
-Product Dimensions: 75"L X 54"W X 11"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with BIRD OF PARADISE 11" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 11"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -4983,15 +4983,15 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE 11" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 11"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 80 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE 11" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 11"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 80 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -5119,15 +5119,15 @@
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE 11" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 39"W X 11"H
-Size: Twin
-Features
-- Supportive coil system for steady alignment
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE 11" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 11"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -5255,13 +5255,13 @@
       </c>
       <c r="G35" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with CATMINT 10" Innerspring Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 54"W X 75"D X 10"H
-Size: Full
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with CATMINT 10" Innerspring Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="22" t="inlineStr">
@@ -5389,13 +5389,13 @@
       </c>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CATMINT 10" Innerspring Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 10"H
-Size: Queen
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 90.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CATMINT 10" Innerspring Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 90.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="22" t="inlineStr">
@@ -5523,13 +5523,13 @@
       </c>
       <c r="G37" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CATMINT 10" Innerspring Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 39"W X 75"D X 10"H
-Size: Twin
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 58.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CATMINT 10" Innerspring Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 10"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 58.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" s="22" t="inlineStr">
@@ -5657,15 +5657,15 @@
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with CATMINT 12" Innerspring Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 54"W X 75"D X 12"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 82.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with CATMINT 12" Innerspring Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 82.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -5793,15 +5793,15 @@
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CATMINT 12" Innerspring Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 121.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CATMINT 12" Innerspring Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 121.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -5929,15 +5929,15 @@
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CATMINT 12" Innerspring Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 39"W X 75"D X 12"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 62.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CATMINT 12" Innerspring Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 12"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 62.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -6065,16 +6065,16 @@
       </c>
       <c r="G41" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 10" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 76"W X 80"D X 10"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 66.77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 10" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 10"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 66.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" s="26" t="inlineStr">
@@ -6202,16 +6202,16 @@
       </c>
       <c r="G42" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with COREOPSIS 10" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 54"W X 75"D X 10"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 46.77 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with COREOPSIS 10" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 46.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" s="26" t="inlineStr">
@@ -6339,16 +6339,16 @@
       </c>
       <c r="G43" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 10" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 10"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 55.33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 10" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 55.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" s="26" t="inlineStr">
@@ -6476,16 +6476,16 @@
       </c>
       <c r="G44" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 10" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 39"W X 75"D X 10"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 37.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 10" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 10"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 37.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="26" t="inlineStr">
@@ -6613,16 +6613,16 @@
       </c>
       <c r="G45" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with COREOPSIS 12" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 76"W X 80"D X 12"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 83.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with COREOPSIS 12" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 83.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="28" t="inlineStr">
@@ -6750,16 +6750,16 @@
       </c>
       <c r="G46" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 12" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"D X 12"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 57.86 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 12" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 57.86 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" s="28" t="inlineStr">
@@ -6887,16 +6887,16 @@
       </c>
       <c r="G47" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 12" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 69.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 12" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 69.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" s="28" t="inlineStr">
@@ -7024,16 +7024,16 @@
       </c>
       <c r="G48" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with COREOPSIS 12" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 12"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 43.32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with COREOPSIS 12" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 12"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 43.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
@@ -7161,16 +7161,16 @@
       </c>
       <c r="G49" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 8" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 76"W X 80"D X 8"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 57.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 8" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 8"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 57.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="30" t="inlineStr">
@@ -7298,16 +7298,16 @@
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 8" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 54"W X 75"D X 8"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 39.31 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 8" Memory Foam Wave Comfort is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 39.31 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="30" t="inlineStr">
@@ -7435,16 +7435,16 @@
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with COREOPSIS 8" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 60"W X 80"D X 8"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 47.96 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with COREOPSIS 8" Memory Foam Wave Comfort, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 47.96 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" s="30" t="inlineStr">
@@ -7572,16 +7572,16 @@
       </c>
       <c r="G52" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COREOPSIS 8" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 39"W X 75"D X 8"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 30.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COREOPSIS 8" Memory Foam Wave Comfort offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 30.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" s="30" t="inlineStr">
@@ -7709,13 +7709,13 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAISY 6" Bunkie Board Combo Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 3-Layer Quilting, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 54"W X 6"H
-Size: Full
-Materials: 3-Layer Quilting.
-Color: White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAISY 6" Bunkie Board Combo Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 3-Layer Quilting, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 6"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: 3-Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -7843,13 +7843,13 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with DAISY 6" Bunkie Board Combo Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 3-Layer Quilting construction keeps you comfortable, finished in White tones.
-Product Dimensions: 75"L X 39"W X 6"H
-Size: Twin
-Materials: 3-Layer Quilting.
-Color: White
-Weight: 40 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with DAISY 6" Bunkie Board Combo Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 3-Layer Quilting construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 6"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: 3-Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 40 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAISY 6" Bunkie Board Combo Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.
-Product Dimensions: 80"L X 39"W X 6"H
-Size: Twin XL
-Color: White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAISY 6" Bunkie Board Combo Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 39"W X 6"H&lt;br&gt;
+Size: Twin XL&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -8106,13 +8106,13 @@
       </c>
       <c r="G56" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAISY 8" Bunkie Board Combo Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 3-Layer Quilting, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 54"W X 8"H
-Size: Full
-Materials: 3-Layer Quilting.
-Color: White
-Weight: 65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAISY 8" Bunkie Board Combo Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 3-Layer Quilting, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: 3-Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="33" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="G57" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with DAISY 8" Bunkie Board Combo Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.
-Product Dimensions: 80"L X 54"W X 8"H
-Size: Full
-Color: White
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with DAISY 8" Bunkie Board Combo Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 54"W X 8"H&lt;br&gt;
+Size: Full&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="33" t="inlineStr">
@@ -8369,13 +8369,13 @@
       </c>
       <c r="G58" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAISY 8" Bunkie Board Combo Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 3-Layer Quilting, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 8"H
-Size: Queen
-Materials: 3-Layer Quilting.
-Color: White
-Weight: 75 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAISY 8" Bunkie Board Combo Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 3-Layer Quilting, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: 3-Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="33" t="inlineStr">
@@ -8503,13 +8503,13 @@
       </c>
       <c r="G59" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAISY 8" Bunkie Board Combo Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 3-Layer Quilting, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 39"W X 8"H
-Size: Twin
-Materials: 3-Layer Quilting.
-Color: White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAISY 8" Bunkie Board Combo Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 3-Layer Quilting, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: 3-Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="33" t="inlineStr">
@@ -8637,15 +8637,15 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DERRY 4" Size Memory Foam Trundle Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.
-Product Dimensions: 75"L X 38"W X 4"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Color: White
-Weight: 20 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DERRY 4" Size Memory Foam Trundle Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 75"L X 38"W X 4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8766,15 +8766,15 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 10" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 72"W X 84"D X 12"H
-Size: California King
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 59 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 10" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 72"W X 84"D X 12"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 59 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -8902,15 +8902,15 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with EDELWEISS 10" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 76"L X 80"W X 10"H
-Size: Eastern King
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 59 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with EDELWEISS 10" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 76"L X 80"W X 10"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 59 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -9038,15 +9038,15 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 10" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"L X 75"W X 10"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 40 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 10" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"L X 75"W X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 40 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -9174,15 +9174,15 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 10" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"L X 80"W X 10"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 10" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"L X 80"W X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -9310,15 +9310,15 @@
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with EDELWEISS 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 72"W X 84"D X 12"H
-Size: California King
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 118 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with EDELWEISS 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 72"W X 84"D X 12"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 118 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" s="35" t="inlineStr">
@@ -9446,15 +9446,15 @@
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 12" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 76"L X 80"L X 12"H
-Size: Eastern King
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 72 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 12" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 76"L X 80"L X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 72 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" s="35" t="inlineStr">
@@ -9582,15 +9582,15 @@
       </c>
       <c r="G67" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 12" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 54"L X 75"W X 12"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 49 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 12" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 54"L X 75"W X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 49 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="35" t="inlineStr">
@@ -9718,15 +9718,15 @@
       </c>
       <c r="G68" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with EDELWEISS 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 60"L X 80"W X 12"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 57 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with EDELWEISS 12" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 60"L X 80"W X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="35" t="inlineStr">
@@ -9854,15 +9854,15 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 6" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"L X 75"W X 6"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 6" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"L X 75"W X 6"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -9990,15 +9990,15 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 6" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 39"L X 75"W X 6"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 18 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 6" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 39"L X 75"W X 6"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -10126,15 +10126,15 @@
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with EDELWEISS 8" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 54"L X 75"W X 6"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with EDELWEISS 8" Memory Foam Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 54"L X 75"W X 6"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr">
@@ -10262,15 +10262,15 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 8" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 60"L X 80"W X 8"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 39 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 8" Memory Foam Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"L X 80"W X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 39 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -10398,15 +10398,15 @@
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDELWEISS 8" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 39"L X 75"W X 8"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDELWEISS 8" Memory Foam Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 39"L X 75"W X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr">
@@ -10534,15 +10534,15 @@
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDREA 10" Tight Top Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 84"L X 72"W X 10"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDREA 10" Tight Top Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 10"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" s="16" t="inlineStr">
@@ -10670,15 +10670,15 @@
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with EDREA 10" Tight Top Pocket Coil, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 80"L X 76"W X 10"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with EDREA 10" Tight Top Pocket Coil, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 10"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="16" t="inlineStr">
@@ -10806,15 +10806,15 @@
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDREA 10" Tight Top Pocket Coil offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 75"L X 54"W X 10"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDREA 10" Tight Top Pocket Coil offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="16" t="inlineStr">
@@ -10942,15 +10942,15 @@
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EDREA 10" Tight Top Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 80"L X 60"W X 10"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EDREA 10" Tight Top Pocket Coil is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Stretch Knit Fabric 4 Layer Continuous Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="16" t="inlineStr">
@@ -11078,15 +11078,15 @@
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELBERTYNA 8" Tight Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 84"L X 72"W X 8"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELBERTYNA 8" Tight Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 8"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
@@ -11214,15 +11214,15 @@
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELBERTYNA 8" Tight Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 80"L X 76"W X 8"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELBERTYNA 8" Tight Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 8"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
@@ -11350,15 +11350,15 @@
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ELBERTYNA 8" Tight Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam construction keeps you comfortable, finished in White tones.
-Product Dimensions: 75"L X 54"W X 8"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ELBERTYNA 8" Tight Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" s="18" t="inlineStr">
@@ -11486,15 +11486,15 @@
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELBERTYNA 8" Tight Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 8"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELBERTYNA 8" Tight Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" s="18" t="inlineStr">
@@ -11622,15 +11622,15 @@
       </c>
       <c r="G82" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELBERTYNA 8" Tight Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 39"W X 8"H
-Size: Twin
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 40 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELBERTYNA 8" Tight Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1 or 2" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 40 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" s="18" t="inlineStr">
@@ -11758,16 +11758,16 @@
       </c>
       <c r="G83" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 10" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 76"W X 80"D X 10"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 74.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 10" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 10"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 74.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H83" s="20" t="inlineStr">
@@ -11895,16 +11895,16 @@
       </c>
       <c r="G84" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 10" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 54"W X 75"D X 10"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 50.69 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 10" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50.69 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H84" s="20" t="inlineStr">
@@ -12032,16 +12032,16 @@
       </c>
       <c r="G85" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FORSYTHIA 10" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 60"W X 80"D X 10"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 59.88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FORSYTHIA 10" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 59.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H85" s="20" t="inlineStr">
@@ -12169,16 +12169,16 @@
       </c>
       <c r="G86" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 10" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 39"W X 75"D X 10"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 39.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 10" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 10"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 39.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H86" s="20" t="inlineStr">
@@ -12306,16 +12306,16 @@
       </c>
       <c r="G87" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 12" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 76"W X 80"D X 12"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 87.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 12" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 87.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H87" s="38" t="inlineStr">
@@ -12443,16 +12443,16 @@
       </c>
       <c r="G88" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FORSYTHIA 12" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 54"W X 75"D X 12"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 60.24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FORSYTHIA 12" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60.24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H88" s="38" t="inlineStr">
@@ -12580,16 +12580,16 @@
       </c>
       <c r="G89" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 12" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 71.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 12" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 71.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H89" s="38" t="inlineStr">
@@ -12717,16 +12717,16 @@
       </c>
       <c r="G90" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 12" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 39"W X 75"D X 12"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 44.99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 12" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 12"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 44.99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H90" s="38" t="inlineStr">
@@ -12854,16 +12854,16 @@
       </c>
       <c r="G91" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FORSYTHIA 8" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 76"W X 80"D X 8"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 60.28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FORSYTHIA 8" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 8"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60.28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" s="22" t="inlineStr">
@@ -12991,16 +12991,16 @@
       </c>
       <c r="G92" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 8" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"D X 8"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 41.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 8" Green Tea Gel Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 41.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" s="22" t="inlineStr">
@@ -13128,16 +13128,16 @@
       </c>
       <c r="G93" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FORSYTHIA 8" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"W X 80"D X 8"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 51.04 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FORSYTHIA 8" Green Tea Gel Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 51.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H93" s="22" t="inlineStr">
@@ -13265,16 +13265,16 @@
       </c>
       <c r="G94" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FORSYTHIA 8" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 8"H
-Size: Twin
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 32.34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FORSYTHIA 8" Green Tea Gel Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 32.34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H94" s="22" t="inlineStr">
@@ -13402,15 +13402,15 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLLYHOCK 3" Tri-Fold Memory Foam Topper is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 52"W X 73"D X 3"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 20.55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLLYHOCK 3" Tri-Fold Memory Foam Topper is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 52"W X 73"D X 3"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 20.55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
@@ -13538,15 +13538,15 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with HOLLYHOCK 3" Tri-Fold Memory Foam Topper, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 60"W X 80"D X 3"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 23.32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with HOLLYHOCK 3" Tri-Fold Memory Foam Topper, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 3"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 23.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -13674,15 +13674,15 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLLYHOCK 3" Tri-Fold Memory Foam Topper offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 38"W X 75"D X 3"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 15.64 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLLYHOCK 3" Tri-Fold Memory Foam Topper offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 38"W X 75"D X 3"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 15.64 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -13810,15 +13810,15 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLLYHOCK 3" Tri-Fold Memory Foam Topper is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 38"W X 78"D X 3"H
-Size: TXL
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 15.97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLLYHOCK 3" Tri-Fold Memory Foam Topper is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 38"W X 78"D X 3"H&lt;br&gt;
+Size: TXL&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 15.97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -13946,15 +13946,15 @@
       </c>
       <c r="G99" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with HOLLYHOCK 4" Tri-Fold Memory Foam Topper, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 52"W X 73"D X 4"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 24.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with HOLLYHOCK 4" Tri-Fold Memory Foam Topper, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 52"W X 73"D X 4"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 24.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" s="33" t="inlineStr">
@@ -14082,15 +14082,15 @@
       </c>
       <c r="G100" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLLYHOCK 4" Tri-Fold Memory Foam Topper offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 4"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 27.94 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLLYHOCK 4" Tri-Fold Memory Foam Topper offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 4"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 27.94 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" s="33" t="inlineStr">
@@ -14218,15 +14218,15 @@
       </c>
       <c r="G101" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLLYHOCK 4" Tri-Fold Memory Foam Topper is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 38"W X 75"D X 4"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 18.35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLLYHOCK 4" Tri-Fold Memory Foam Topper is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 38"W X 75"D X 4"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 18.35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="33" t="inlineStr">
@@ -14354,15 +14354,15 @@
       </c>
       <c r="G102" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with HOLLYHOCK 4" Tri-Fold Memory Foam Topper, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 38"W X 78"D X 4"H
-Size: TXL
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White or Gray
-Weight: 18.85 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with HOLLYHOCK 4" Tri-Fold Memory Foam Topper, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 38"W X 78"D X 4"H&lt;br&gt;
+Size: TXL&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 18.85 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" s="33" t="inlineStr">
@@ -14490,15 +14490,15 @@
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JALEN 9" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 84"L X 72"W X 9"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JALEN 9" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 9"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -14626,15 +14626,15 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JALEN 9" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 80"L X 76"W X 9"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JALEN 9" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 9"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -14762,15 +14762,15 @@
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with JALEN 9" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam construction keeps you comfortable, finished in White tones.
-Product Dimensions: 75"L X 54"W X 9"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with JALEN 9" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 9"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -14898,15 +14898,15 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JALEN 9" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 9"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JALEN 9" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 9"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -15034,15 +15034,15 @@
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JALEN 9" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 39"W X 9"H
-Size: Twin
-Features
-- Supportive coil system for steady alignment
-Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.
-Color: White
-Weight: 40 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JALEN 9" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 9"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 or 2" Of Innerspring Support Base Foam, 1" Of Comfort Layer Hd Polyurethane Foam.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 40 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -15170,15 +15170,15 @@
       </c>
       <c r="G108" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with LILIUM 13" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.
-Product Dimensions: 80"L X 60"W X 13"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 75 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with LILIUM 13" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 13"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" s="35" t="inlineStr">
@@ -15306,15 +15306,15 @@
       </c>
       <c r="G109" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LILIUM 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it is finished in White or Brown tones and made for lasting comfort.
-Product Dimensions: 84"L X 72"W X 13"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 90 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LILIUM 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it is finished in White or Brown tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 13"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 90 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" s="35" t="inlineStr">
@@ -15442,15 +15442,15 @@
       </c>
       <c r="G110" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LILIUM 13" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White or Brown tones.
-Product Dimensions: 80"L X 76"W X 13"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 90 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LILIUM 13" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White or Brown tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 13"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 90 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" s="35" t="inlineStr">
@@ -15578,15 +15578,15 @@
       </c>
       <c r="G111" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with LILIUM 13" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.
-Product Dimensions: 75"L X 54"W X 13"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 65 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with LILIUM 13" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 13"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 65 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H111" s="35" t="inlineStr">
@@ -15714,15 +15714,15 @@
       </c>
       <c r="G112" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LILIUM 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it is finished in White or Brown tones and made for lasting comfort.
-Product Dimensions: 75"L X 39"W X 13"H
-Size: Twin
-Features
-- Supportive coil system for steady alignment
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LILIUM 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it is finished in White or Brown tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 13"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H112" s="35" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MADDER 4" Trundle Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.
-Product Dimensions: 74"L X37.5"W X 4"H
-Size: Twin
-Color: White
-Weight: 10 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MADDER 4" Trundle Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 74"L X37.5"W X 4"H&lt;br&gt;
+Size: Twin&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -15976,13 +15976,13 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with MADDER 6" Trundle Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: 3 or 4" Quilted Printed Knit construction keeps you comfortable, finished in White tones.
-Product Dimensions: 72"L X38"W X 6"H
-Size: Twin
-Materials: Quilting: 3 or 4" Quilted Printed Knit.
-Color: White
-Weight: 15 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with MADDER 6" Trundle Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: 3 or 4" Quilted Printed Knit construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 72"L X38"W X 6"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: 3 or 4" Quilted Printed Knit.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -16108,15 +16108,15 @@
       </c>
       <c r="G115" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 76"W X 80"D X 10"H
-Size: Eastern King
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 74.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 10"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 74.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H115" s="16" t="inlineStr">
@@ -16244,15 +16244,15 @@
       </c>
       <c r="G116" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 54"W X 75"D X 10"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 50.69 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 10"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50.69 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" s="16" t="inlineStr">
@@ -16380,15 +16380,15 @@
       </c>
       <c r="G117" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 60"W X 80"D X 10"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 59.88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 10"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 59.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" s="16" t="inlineStr">
@@ -16516,15 +16516,15 @@
       </c>
       <c r="G118" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 39"W X 75"D X 10"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 39.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 10" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 10"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 39.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" s="16" t="inlineStr">
@@ -16652,15 +16652,15 @@
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 76"W X 80"D X 12"H
-Size: Eastern King
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 87.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 87.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" s="18" t="inlineStr">
@@ -16788,15 +16788,15 @@
       </c>
       <c r="G120" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 54"W X 75"D X 12"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 60.24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60.24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" s="18" t="inlineStr">
@@ -16924,15 +16924,15 @@
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 71.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 71.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" s="18" t="inlineStr">
@@ -17060,15 +17060,15 @@
       </c>
       <c r="G122" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 39"W X 75"D X 12"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 44.99 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 12" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 12"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 44.99 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H122" s="18" t="inlineStr">
@@ -17196,15 +17196,15 @@
       </c>
       <c r="G123" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 76"W X 80"D X 8"H
-Size: Eastern King
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 60.28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 8"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60.28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H123" s="20" t="inlineStr">
@@ -17332,15 +17332,15 @@
       </c>
       <c r="G124" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"D X 8"H
-Size: Full
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 41.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Inner Cover: Cotton Scrim Fabric, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 8"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 41.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H124" s="20" t="inlineStr">
@@ -17468,15 +17468,15 @@
       </c>
       <c r="G125" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 60"W X 80"D X 8"H
-Size: Queen
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 51.04 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Inner Cover: Cotton Scrim Fabric, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 8"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 51.04 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H125" s="20" t="inlineStr">
@@ -17604,15 +17604,15 @@
       </c>
       <c r="G126" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.
-Product Dimensions: 39"W X 75"D X 8"H
-Size: Twin
-Features
-- Memory foam comfort layer
-Materials: Inner Cover: Cotton Scrim Fabric.
-Color: White
-Weight: 32.34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with NASTURTIUM 8" Bamboo Charcoal Infused Memory Foam, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Inner Cover: Cotton Scrim Fabric construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 39"W X 75"D X 8"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Memory foam comfort layer&lt;/p&gt;
+&lt;p&gt;Materials: Inner Cover: Cotton Scrim Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 32.34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H126" s="20" t="inlineStr">
@@ -17740,15 +17740,15 @@
       </c>
       <c r="G127" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SALVIA 12" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 72"W X 84"D X 12"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 118 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SALVIA 12" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 72"W X 84"D X 12"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 118 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H127" s="38" t="inlineStr">
@@ -17876,15 +17876,15 @@
       </c>
       <c r="G128" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SALVIA 12" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 76"W X 80"D X 12"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 118 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SALVIA 12" Euro Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 118 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H128" s="38" t="inlineStr">
@@ -18012,15 +18012,15 @@
       </c>
       <c r="G129" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with SALVIA 12" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 54"W X 75"D X 12"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 80 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with SALVIA 12" Euro Top Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 80 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H129" s="38" t="inlineStr">
@@ -18148,15 +18148,15 @@
       </c>
       <c r="G130" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SALVIA 12" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 94 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SALVIA 12" Euro Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 94 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H130" s="38" t="inlineStr">
@@ -18284,15 +18284,15 @@
       </c>
       <c r="G131" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SIDDALEE 16" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 84"L X 72"W X 16"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.
-Color: White or Gray
-Weight: 100 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SIDDALEE 16" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 16"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 100 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H131" s="22" t="inlineStr">
@@ -18420,15 +18420,15 @@
       </c>
       <c r="G132" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with SIDDALEE 16" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 80"L X 76"W X 16"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.
-Color: White or Gray
-Weight: 100 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with SIDDALEE 16" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 16"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 100 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H132" s="22" t="inlineStr">
@@ -18556,15 +18556,15 @@
       </c>
       <c r="G133" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SIDDALEE 16" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 75"L X 54"W X 16"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.
-Color: White or Gray
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SIDDALEE 16" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 16"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H133" s="22" t="inlineStr">
@@ -18692,15 +18692,15 @@
       </c>
       <c r="G134" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SIDDALEE 16" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 80"L X 60"W X 16"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.
-Color: White or Gray
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SIDDALEE 16" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 16"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: Designer Organic Cotton Fabric 5 Layer Tack or Jump Quilting Hd Polyurethan Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H134" s="22" t="inlineStr">
@@ -18828,15 +18828,15 @@
       </c>
       <c r="G135" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STORMIN 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 84"L X 72"W X 13"H
-Size: California King
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 90 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STORMIN 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 13"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 90 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H135" s="30" t="inlineStr">
@@ -18964,15 +18964,15 @@
       </c>
       <c r="G136" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STORMIN 13" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.
-Product Dimensions: 80"L X 76"W X 13"H
-Size: Eastern King
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 90 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STORMIN 13" Euro Pillow Top Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam, it brings a reliable, comfortable feel with White or Gray tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 13"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 90 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H136" s="30" t="inlineStr">
@@ -19100,15 +19100,15 @@
       </c>
       <c r="G137" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with STORMIN 13" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam construction keeps you comfortable, finished in White or Gray tones.
-Product Dimensions: 75"L X 54"W X 13"H
-Size: Full
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with STORMIN 13" Euro Pillow Top Mattress, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam construction keeps you comfortable, finished in White or Gray tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 13"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H137" s="30" t="inlineStr">
@@ -19236,15 +19236,15 @@
       </c>
       <c r="G138" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STORMIN 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 13"H
-Size: Queen
-Features
-- Supportive coil system for steady alignment
-Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.
-Color: White or Gray
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STORMIN 13" Euro Pillow Top Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam, it is finished in White or Gray tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 13"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Quilting: 5 Layer Tack or Jump Quilting Hd Polyurethane Foam.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H138" s="30" t="inlineStr">
@@ -19372,17 +19372,17 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with VERBENA 12" Hybrid Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 72"W X 84"D X 12"H
-Size: California King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 118 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with VERBENA 12" Hybrid Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 72"W X 84"D X 12"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 118 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H139" s="8" t="inlineStr">
@@ -19510,17 +19510,17 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERBENA 12" Hybrid Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 76"W X 80"D X 12"H
-Size: Eastern King
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 104 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERBENA 12" Hybrid Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 76"W X 80"D X 12"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 104 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H140" s="8" t="inlineStr">
@@ -19648,17 +19648,17 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERBENA 12" Hybrid Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 54"W X 75"D X 12"H
-Size: Full
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 69 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERBENA 12" Hybrid Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 54"W X 75"D X 12"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 69 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
@@ -19786,17 +19786,17 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with VERBENA 12" Hybrid Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.
-Product Dimensions: 60"W X 80"D X 12"H
-Size: Queen
-Features
-- Cooling gel infusion for a fresher sleep
-- Memory foam comfort layer
-- Supportive coil system for steady alignment
-Materials: Safety: CFR 1633 &amp; CFR 1632, CAN CGG SB 4.5-27.7.
-Color: White
-Weight: 82 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with VERBENA 12" Hybrid Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7 construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"D X 12"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cooling gel infusion for a fresher sleep&lt;br&gt;
+- Memory foam comfort layer&lt;br&gt;
+- Supportive coil system for steady alignment&lt;/p&gt;
+&lt;p&gt;Materials: Safety: CFR 1633 &amp;amp; CFR 1632, CAN CGG SB 4.5-27.7.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 82 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="8" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="G143" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AKSEL Futon Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Cotton, Polyester, it brings a reliable, comfortable feel with Khaki or Brown tones.
-Product Dimensions: 71"L X 51"W X 6"H
-Materials: Cotton, Polyester.
-Color: Khaki or Brown
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AKSEL Futon Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Cotton, Polyester, it brings a reliable, comfortable feel with Khaki or Brown tones.&lt;br&gt;
+Product Dimensions: 71"L X 51"W X 6"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Khaki or Brown&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H143" s="33" t="inlineStr">
@@ -20049,12 +20049,12 @@
       </c>
       <c r="G144" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with AKSEL Futon Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Cotton, Polyester construction keeps you comfortable, finished in Black or Red tones.
-Product Dimensions: 71"L X 51"W X 6"H
-Materials: Cotton, Polyester.
-Color: Black or Red
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with AKSEL Futon Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Cotton, Polyester construction keeps you comfortable, finished in Black or Red tones.&lt;br&gt;
+Product Dimensions: 71"L X 51"W X 6"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Black or Red&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" s="33" t="inlineStr">
@@ -20178,12 +20178,12 @@
       </c>
       <c r="G145" s="33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AKSEL Futon Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Cotton, Polyester, it is finished in Gray or Navy tones and made for lasting comfort.
-Product Dimensions: 71"L X 51"W X 6"H
-Materials: Cotton, Polyester.
-Color: Gray or Navy
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AKSEL Futon Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Cotton, Polyester, it is finished in Gray or Navy tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 71"L X 51"W X 6"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Gray or Navy&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="33" t="inlineStr">
@@ -20310,12 +20310,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with KNOX 6" Black Futon Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Cotton, Polyester construction keeps you comfortable, finished in Black tones.
-Product Dimensions: 71"L X 51"W X 6"H
-Materials: Cotton, Polyester.
-Color: Black
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with KNOX 6" Black Futon Mattress, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Cotton, Polyester construction keeps you comfortable, finished in Black tones.&lt;br&gt;
+Product Dimensions: 71"L X 51"W X 6"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -20436,12 +20436,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KNOX 8" Black Futon Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Cotton, Polyester, it is finished in Black tones and made for lasting comfort.
-Product Dimensions: 71"L X 51"W X 8"H
-Materials: Cotton, Polyester.
-Color: Black
-Weight: 35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KNOX 8" Black Futon Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Cotton, Polyester, it is finished in Black tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 71"L X 51"W X 8"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -20562,12 +20562,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KNOX 8" Black Futon Mattress w/ Inner Spring is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Cotton, Polyester, it brings a reliable, comfortable feel with Black tones.
-Product Dimensions: 72"L X 51"W X 8"H
-Materials: Cotton, Polyester.
-Color: Black
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KNOX 8" Black Futon Mattress w/ Inner Spring is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Cotton, Polyester, it brings a reliable, comfortable feel with Black tones.&lt;br&gt;
+Product Dimensions: 72"L X 51"W X 8"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -20688,12 +20688,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with KNOX 8" Red or Black Futon Mattress w/ Inner Spring, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Cotton, Polyester construction keeps you comfortable, finished in Black or Red tones.
-Product Dimensions: 72"L X 51"W X 8"H
-Materials: Cotton, Polyester.
-Color: Black or Red
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with KNOX 8" Red or Black Futon Mattress w/ Inner Spring, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Cotton, Polyester construction keeps you comfortable, finished in Black or Red tones.&lt;br&gt;
+Product Dimensions: 72"L X 51"W X 8"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: Black or Red&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -20814,12 +20814,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KNOX 8" White Futon Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Cotton, Polyester, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 71"L X 51"W X 8"H
-Materials: Cotton, Polyester.
-Color: White
-Weight: 35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KNOX 8" White Futon Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Cotton, Polyester, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 71"L X 51"W X 8"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -20940,12 +20940,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KNOX 8" White Futon Mattress w/ Inner Spring is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Cotton, Polyester, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 72"L X 51"W X 8"H
-Materials: Cotton, Polyester.
-Color: White
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KNOX 8" White Futon Mattress w/ Inner Spring is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Cotton, Polyester, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 72"L X 51"W X 8"H&lt;/p&gt;
+&lt;p&gt;Materials: Cotton, Polyester.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -21071,12 +21071,12 @@
       </c>
       <c r="G152" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALEKSA Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 84"L X 72"W X 7"H
-Size: California King
-Color: Gray
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALEKSA Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 7"H&lt;br&gt;
+Size: California King&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="35" t="inlineStr">
@@ -21200,12 +21200,12 @@
       </c>
       <c r="G153" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALEKSA Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 80"L X 76"W X 7"H
-Size: Eastern King
-Color: Gray
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALEKSA Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 7"H&lt;br&gt;
+Size: Eastern King&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="35" t="inlineStr">
@@ -21329,12 +21329,12 @@
       </c>
       <c r="G154" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with ALEKSA Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 75"L X 54"W X 7"H
-Size: Full
-Color: Gray
-Weight: 45 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with ALEKSA Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 7"H&lt;br&gt;
+Size: Full&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 45 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="35" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="G155" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALEKSA Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 80"L X 60"W X 7"H
-Size: Queen
-Color: Gray
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALEKSA Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 7"H&lt;br&gt;
+Size: Queen&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" s="35" t="inlineStr">
@@ -21587,13 +21587,13 @@
       </c>
       <c r="G156" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with BIRD OF PARADISE Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White tones.
-Product Dimensions: 84"L X 72"W X 7"H
-Size: California King
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with BIRD OF PARADISE Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 7"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" s="38" t="inlineStr">
@@ -21721,13 +21721,13 @@
       </c>
       <c r="G157" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 80"L X 76"W X 7"H
-Size: Eastern King
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 7"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H157" s="38" t="inlineStr">
@@ -21855,13 +21855,13 @@
       </c>
       <c r="G158" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 54"W X 7"H
-Size: Full
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 40 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 7"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 40 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" s="38" t="inlineStr">
@@ -21989,13 +21989,13 @@
       </c>
       <c r="G159" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with BIRD OF PARADISE Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White tones.
-Product Dimensions: 80"L X 60"W X 7"H
-Size: Queen
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with BIRD OF PARADISE Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 7"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="38" t="inlineStr">
@@ -22123,13 +22123,13 @@
       </c>
       <c r="G160" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIRD OF PARADISE Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 75"L X 39"W X 7"H
-Size: Twin
-Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.
-Color: White
-Weight: 30 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIRD OF PARADISE Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 7"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Double Layer Of Hd Polyurethane Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 30 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" s="38" t="inlineStr">
@@ -22257,13 +22257,13 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LILIUM Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White or Brown tones.
-Product Dimensions: 84"L X 72"W X 7"H
-Size: California King
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LILIUM Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White or Brown tones.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 7"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -22391,13 +22391,13 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with LILIUM Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.
-Product Dimensions: 80"L X 76"W X 7"H
-Size: Eastern King
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 60 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with LILIUM Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 7"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 60 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -22525,13 +22525,13 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LILIUM Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it is finished in White or Brown tones and made for lasting comfort.
-Product Dimensions: 75"L X 54"W X 7"H
-Size: Full
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 45 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LILIUM Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it is finished in White or Brown tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 7"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 45 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -22659,13 +22659,13 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LILIUM Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White or Brown tones.
-Product Dimensions: 80"L X 60"W X 7"H
-Size: Queen
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LILIUM Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber, it brings a reliable, comfortable feel with White or Brown tones.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 7"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -22793,13 +22793,13 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with LILIUM Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.
-Product Dimensions: 75"L X 39"W X 7"H
-Size: Twin
-Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.
-Color: White or Brown
-Weight: 10 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with LILIUM Foundation, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber construction keeps you comfortable, finished in White or Brown tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 7"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: 1 Oz High Resilience H87 Polyester Fiberfill Foam Separated With Polyester Fiber.&lt;br&gt;
+Color: White or Brown&lt;br&gt;
+Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -22922,12 +22922,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS 39" Pop Up Trundle is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.
-Product Dimensions: 70"L X 38 1/2"W X 16"H
-Materials: Steel.
-Color: Black
-Weight: 53 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS 39" Pop Up Trundle is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.&lt;br&gt;
+Product Dimensions: 70"L X 38 1/2"W X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 53 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -23053,13 +23053,13 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS 39" Top Spring, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black tones.
-Product Dimensions: 77"L X 39"W X 5"H
-Size: Twin
-Materials: Steel.
-Color: Black
-Weight: 28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS 39" Top Spring, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black tones.&lt;br&gt;
+Product Dimensions: 77"L X 39"W X 5"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -23185,13 +23185,13 @@
       </c>
       <c r="G168" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS 76" or Full Bolt offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Black tones and made for lasting comfort.
-Product Dimensions: 75"L X 5"W X 2"H
-Size: Twin
-Materials: Steel.
-Color: Black
-Weight: 13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS 76" or Full Bolt offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Black tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 75"L X 5"W X 2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H168" s="24" t="inlineStr">
@@ -23319,13 +23319,13 @@
       </c>
       <c r="G169" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS 76" or Full Hook is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.
-Product Dimensions: 75"L X 6"W X 3"H
-Size: Twin
-Materials: Steel.
-Color: Black
-Weight: 13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS 76" or Full Hook is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.&lt;br&gt;
+Product Dimensions: 75"L X 6"W X 3"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H169" s="24" t="inlineStr">
@@ -23453,13 +23453,13 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS 82" Bolt, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black tones.
-Product Dimensions: 81"L X 5"W X 2"H
-Size: Queen
-Materials: Steel.
-Color: Black
-Weight: 15 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS 82" Bolt, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black tones.&lt;br&gt;
+Product Dimensions: 81"L X 5"W X 2"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -23585,13 +23585,13 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS 82" Hook offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Black tones and made for lasting comfort.
-Product Dimensions: 81"L X 6"W X 3"H
-Size: Queen
-Materials: Steel.
-Color: Black
-Weight: 14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS 82" Hook offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Black tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 81"L X 6"W X 3"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -23717,13 +23717,13 @@
       </c>
       <c r="G172" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Base Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Silver tones.
-Product Dimensions: 72"W X 84"L X 14"H
-Size: California King
-Materials: Steel.
-Color: Silver
-Weight: 53 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Base Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Silver tones.&lt;br&gt;
+Product Dimensions: 72"W X 84"L X 14"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 53 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H172" s="28" t="inlineStr">
@@ -23851,13 +23851,13 @@
       </c>
       <c r="G173" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS Base Foundation, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Silver tones.
-Product Dimensions: 76"W X 80"L X 14"H
-Size: Eastern King
-Materials: Steel.
-Color: Silver
-Weight: 54 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS Base Foundation, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Silver tones.&lt;br&gt;
+Product Dimensions: 76"W X 80"L X 14"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 54 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H173" s="28" t="inlineStr">
@@ -23985,13 +23985,13 @@
       </c>
       <c r="G174" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Base Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Silver tones and made for lasting comfort.
-Product Dimensions: 54"W X 75"L X 14"H
-Size: Twin XL
-Materials: Steel.
-Color: Silver
-Weight: 38 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Base Foundation offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Silver tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 54"W X 75"L X 14"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H174" s="28" t="inlineStr">
@@ -24119,13 +24119,13 @@
       </c>
       <c r="G175" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Base Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Silver tones.
-Product Dimensions: 60"W X 80"L X 14"H
-Size: Queen
-Materials: Steel.
-Color: Silver
-Weight: 44 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Base Foundation is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Silver tones.&lt;br&gt;
+Product Dimensions: 60"W X 80"L X 14"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H175" s="28" t="inlineStr">
@@ -24253,13 +24253,13 @@
       </c>
       <c r="G176" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS Base Foundation, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Silver tones.
-Product Dimensions: 38"W X 75"L X 14"H
-Size: Twin
-Materials: Steel.
-Color: Silver
-Weight: 24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS Base Foundation, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Silver tones.&lt;br&gt;
+Product Dimensions: 38"W X 75"L X 14"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H176" s="28" t="inlineStr">
@@ -24387,13 +24387,13 @@
       </c>
       <c r="G177" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Metal Frame offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Metal, it is finished in Black tones and made for lasting comfort.
-Product Dimensions: 76"L X 54"W X 13"H
-Size: Full
-Materials: Metal.
-Color: Black
-Weight: 52.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Metal Frame offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Metal, it is finished in Black tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 76"L X 54"W X 13"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 52.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H177" s="30" t="inlineStr">
@@ -24521,13 +24521,13 @@
       </c>
       <c r="G178" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS or Queen Adjustable Frame (4 Legs) is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.
-Product Dimensions: 70 1/2"L X 54"W X 7"H
-Size: Full
-Materials: Steel.
-Color: Black
-Weight: 24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS or Queen Adjustable Frame (4 Legs) is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.&lt;br&gt;
+Product Dimensions: 70 1/2"L X 54"W X 7"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H178" s="26" t="inlineStr">
@@ -24650,12 +24650,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS Pull-Out Trundle, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black tones.
-Product Dimensions: 70"L X 38 1/2"W X 2 1/2"H
-Materials: Steel.
-Color: Black
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS Pull-Out Trundle, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black tones.&lt;br&gt;
+Product Dimensions: 70"L X 38 1/2"W X 2 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -24781,13 +24781,13 @@
       </c>
       <c r="G180" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Metal Frame offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Metal, it is finished in Black tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 13"H
-Size: Queen
-Materials: Metal.
-Color: Black
-Weight: 61.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Metal Frame offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Metal, it is finished in Black tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 13"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 61.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" s="30" t="inlineStr">
@@ -24915,13 +24915,13 @@
       </c>
       <c r="G181" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS or King Adjustable Frame (4 Legs) is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.
-Product Dimensions: 80"L X 70 1/2"W X 7"H
-Size: Queen
-Materials: Steel.
-Color: Black
-Weight: 26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS or King Adjustable Frame (4 Legs) is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.&lt;br&gt;
+Product Dimensions: 80"L X 70 1/2"W X 7"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" s="26" t="inlineStr">
@@ -25044,12 +25044,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS Rollaway Bed w/ 30" Mattress, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black or White tones.
-Product Dimensions: FRAME: 73 1/2"L X 30"W X 14"H, MATTRESS: 72"L X 37 1/2"W X 5"H"
-Materials: Steel.
-Color: Black or White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS Rollaway Bed w/ 30" Mattress, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Steel construction keeps you comfortable, finished in Black or White tones.&lt;br&gt;
+Product Dimensions: FRAME: 73 1/2"L X 30"W X 14"H, MATTRESS: 72"L X 37 1/2"W X 5"H"&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -25170,12 +25170,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Rollaway Bed w/ 39" Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Black or White tones and made for lasting comfort.
-Product Dimensions: 73 1/2"L X 39"W X 14"H
-Materials: Steel.
-Color: Black or White
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Rollaway Bed w/ 39" Mattress offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Steel, it is finished in Black or White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 73 1/2"L X 39"W X 14"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -25296,12 +25296,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Rollaway Bed w/ 48" Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black or White tones.
-Product Dimensions: FRAME: 73 1/2"L X 48"W X 14"H, MATTRESS: 72"L X 37 1/2"W X 5"H"
-Materials: Steel.
-Color: Black or White
-Weight: 50 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Rollaway Bed w/ 48" Mattress is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black or White tones.&lt;br&gt;
+Product Dimensions: FRAME: 73 1/2"L X 48"W X 14"H, MATTRESS: 72"L X 37 1/2"W X 5"H"&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 50 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -25427,13 +25427,13 @@
       </c>
       <c r="G185" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with FRAMOS Metal Frame, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Metal construction keeps you comfortable, finished in Black tones.
-Product Dimensions: 76"L X 38"W X 13"H
-Size: Twin
-Materials: Metal.
-Color: Black
-Weight: 45 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with FRAMOS Metal Frame, designed to deliver comfort and steady support night after night. Its Frame design keeps the look clean and inviting. The Metal construction keeps you comfortable, finished in Black tones.&lt;br&gt;
+Product Dimensions: 76"L X 38"W X 13"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 45 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H185" s="30" t="inlineStr">
@@ -25561,13 +25561,13 @@
       </c>
       <c r="G186" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS Metal Frame offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Metal, it is finished in Black tones and made for lasting comfort.
-Product Dimensions: 80"L X 38"W X 13"H
-Size: Twin XL
-Materials: Metal.
-Color: Black
-Weight: 46.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS Metal Frame offers a cozy, supportive sleep surface made for everyday comfort. Its Frame design keeps the look clean and inviting. Crafted with Metal, it is finished in Black tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 38"W X 13"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Materials: Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 46.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" s="30" t="inlineStr">
@@ -25695,13 +25695,13 @@
       </c>
       <c r="G187" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRAMOS or Full Adjustable Frame (4 Legs) is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.
-Product Dimensions: 64"L X 54"W X 7"H
-Size: Twin
-Materials: Steel.
-Color: Black
-Weight: 18 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRAMOS or Full Adjustable Frame (4 Legs) is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Frame design keeps the look clean and inviting. Built from Steel, it brings a reliable, comfortable feel with Black tones.&lt;br&gt;
+Product Dimensions: 64"L X 54"W X 7"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H187" s="26" t="inlineStr">
@@ -25829,13 +25829,13 @@
       </c>
       <c r="G188" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE I Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.
-Product Dimensions: 53"W X 73"D X 14"H
-Size: Full
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 123.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE I Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 53"W X 73"D X 14"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 123.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H188" s="24" t="inlineStr">
@@ -25957,13 +25957,13 @@
       </c>
       <c r="G189" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE I Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.
-Product Dimensions: 75"W X 79"D X 14"H
-Size: King
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 169 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE I Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 75"W X 79"D X 14"H&lt;br&gt;
+Size: King&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 169 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H189" s="24" t="inlineStr">
@@ -26091,13 +26091,13 @@
       </c>
       <c r="G190" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with SOMNERSIDE I Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal, Fabric construction keeps you comfortable, finished in Metal, Fabric tones.
-Product Dimensions: 59"W X 79"D X 14"H
-Size: Queen
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 133 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with SOMNERSIDE I Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal, Fabric construction keeps you comfortable, finished in Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 59"W X 79"D X 14"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 133 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H190" s="24" t="inlineStr">
@@ -26225,13 +26225,13 @@
       </c>
       <c r="G191" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE I Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.
-Product Dimensions: 37"W X 79"D X 14"H
-Size: Twin XL
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 98 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE I Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 37"W X 79"D X 14"H&lt;br&gt;
+Size: Twin XL&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H191" s="24" t="inlineStr">
@@ -26359,13 +26359,13 @@
       </c>
       <c r="G192" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE II Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.
-Product Dimensions: 53"W X 73"D X 14"H
-Size: Full Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 149.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE II Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 53"W X 73"D X 14"H&lt;br&gt;
+Size: Full Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 149.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" s="26" t="inlineStr">
@@ -26487,13 +26487,13 @@
       </c>
       <c r="G193" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with SOMNERSIDE II Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal, Fabric construction keeps you comfortable, finished in Metal, Fabric tones.
-Product Dimensions: 75"W X 79"D X 14"H
-Size: King Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 194 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with SOMNERSIDE II Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal, Fabric construction keeps you comfortable, finished in Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 75"W X 79"D X 14"H&lt;br&gt;
+Size: King Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 194 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H193" s="26" t="inlineStr">
@@ -26621,13 +26621,13 @@
       </c>
       <c r="G194" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE II Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.
-Product Dimensions: 59"W X 79"D X 14"H
-Size: Queen Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 164 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE II Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 59"W X 79"D X 14"H&lt;br&gt;
+Size: Queen Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 164 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H194" s="26" t="inlineStr">
@@ -26755,13 +26755,13 @@
       </c>
       <c r="G195" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE II Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.
-Product Dimensions: 37"W X 79"D X 14"H
-Size: Twin XL Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 120 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE II Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 37"W X 79"D X 14"H&lt;br&gt;
+Size: Twin XL Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 120 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H195" s="26" t="inlineStr">
@@ -26889,13 +26889,13 @@
       </c>
       <c r="G196" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with SOMNERSIDE III Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal or Fabric construction keeps you comfortable, finished in Black or Gray or White tones.
-Product Dimensions: 71"W X 83"D X 14"H
-Size: California King Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal or Fabric.
-Color: Black or Gray or White
-Weight: 232.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with SOMNERSIDE III Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal or Fabric construction keeps you comfortable, finished in Black or Gray or White tones.&lt;br&gt;
+Product Dimensions: 71"W X 83"D X 14"H&lt;br&gt;
+Size: California King Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal or Fabric.&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
+Weight: 232.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H196" s="28" t="inlineStr">
@@ -27023,13 +27023,13 @@
       </c>
       <c r="G197" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE III Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.
-Product Dimensions: 53"W X 73"D X 14"H
-Size: Full Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 184.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE III Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal, Fabric, it is finished in Metal, Fabric tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 53"W X 73"D X 14"H&lt;br&gt;
+Size: Full Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 184.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H197" s="28" t="inlineStr">
@@ -27157,13 +27157,13 @@
       </c>
       <c r="G198" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE III Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.
-Product Dimensions: 75"W X 79"D X 14"H
-Size: King Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 235 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE III Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 75"W X 79"D X 14"H&lt;br&gt;
+Size: King Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 235 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H198" s="28" t="inlineStr">
@@ -27291,13 +27291,13 @@
       </c>
       <c r="G199" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with SOMNERSIDE III Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal, Fabric construction keeps you comfortable, finished in Metal, Fabric tones.
-Product Dimensions: 59"W X 79"D X 14"H
-Size: Queen Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 199 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with SOMNERSIDE III Adjustable Bed Frame Base, designed to deliver comfort and steady support night after night. Its Contemporary design keeps the look clean and inviting. The Metal, Fabric construction keeps you comfortable, finished in Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 59"W X 79"D X 14"H&lt;br&gt;
+Size: Queen Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 199 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H199" s="28" t="inlineStr">
@@ -27425,13 +27425,13 @@
       </c>
       <c r="G200" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE III Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal or Fabric, it is finished in Black or White tones and made for lasting comfort.
-Product Dimensions: 35"W X 83"D X 14"H
-Size: Twin Cal.King Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal or Fabric.
-Color: Black or White
-Weight: 143 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE III Adjustable Bed Frame Base offers a cozy, supportive sleep surface made for everyday comfort. Its Contemporary design keeps the look clean and inviting. Crafted with Metal or Fabric, it is finished in Black or White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 35"W X 83"D X 14"H&lt;br&gt;
+Size: Twin Cal.King Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal or Fabric.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 143 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H200" s="28" t="inlineStr">
@@ -27559,13 +27559,13 @@
       </c>
       <c r="G201" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOMNERSIDE III Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.
-Product Dimensions: 37"W X 79"D X 14"H
-Size: Twin XL Bonus storage &amp; convenience features (from matching set pieces): USB Port &amp; Under-Bed Light
-Materials: Metal, Fabric.
-Color: Metal, Fabric
-Weight: 148 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOMNERSIDE III Adjustable Bed Frame Base is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Contemporary design keeps the look clean and inviting. Built from Metal, Fabric, it brings a reliable, comfortable feel with Metal, Fabric tones.&lt;br&gt;
+Product Dimensions: 37"W X 79"D X 14"H&lt;br&gt;
+Size: Twin XL Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port &amp;amp; Under-Bed Light&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Metal, Fabric&lt;br&gt;
+Weight: 148 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H201" s="28" t="inlineStr">
@@ -27693,13 +27693,13 @@
       </c>
       <c r="G202" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LUPINE 2" Bunkie Board offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Multi-Needle Quilt 3 Layer Quilting, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 84"L X 72"W X 2"H
-Size: California King
-Materials: Multi-Needle Quilt 3 Layer Quilting.
-Color: White
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LUPINE 2" Bunkie Board offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Multi-Needle Quilt 3 Layer Quilting, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 84"L X 72"W X 2"H&lt;br&gt;
+Size: California King&lt;/p&gt;
+&lt;p&gt;Materials: Multi-Needle Quilt 3 Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr">
@@ -27827,13 +27827,13 @@
       </c>
       <c r="G203" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LUPINE 2" Bunkie Board is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Multi-Needle Quilt 3 Layer Quilting, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 80"L X 76"W X 2"H
-Size: Eastern King
-Materials: Multi-Needle Quilt 3 Layer Quilting.
-Color: White
-Weight: 47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LUPINE 2" Bunkie Board is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Multi-Needle Quilt 3 Layer Quilting, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 80"L X 76"W X 2"H&lt;br&gt;
+Size: Eastern King&lt;/p&gt;
+&lt;p&gt;Materials: Multi-Needle Quilt 3 Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr">
@@ -27961,13 +27961,13 @@
       </c>
       <c r="G204" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with LUPINE 2" Bunkie Board, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Multi-Needle Quilt 3 Layer Quilting construction keeps you comfortable, finished in White tones.
-Product Dimensions: 75"L X 54"W X 2"H
-Size: Full
-Materials: Multi-Needle Quilt 3 Layer Quilting.
-Color: White
-Weight: 28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with LUPINE 2" Bunkie Board, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. The Multi-Needle Quilt 3 Layer Quilting construction keeps you comfortable, finished in White tones.&lt;br&gt;
+Product Dimensions: 75"L X 54"W X 2"H&lt;br&gt;
+Size: Full&lt;/p&gt;
+&lt;p&gt;Materials: Multi-Needle Quilt 3 Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr">
@@ -28095,13 +28095,13 @@
       </c>
       <c r="G205" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LUPINE 2" Bunkie Board offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Multi-Needle Quilt 3 Layer Quilting, it is finished in White tones and made for lasting comfort.
-Product Dimensions: 80"L X 60"W X 2"H
-Size: Queen
-Materials: Multi-Needle Quilt 3 Layer Quilting.
-Color: White
-Weight: 33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LUPINE 2" Bunkie Board offers a cozy, supportive sleep surface made for everyday comfort. Its Mattress design keeps the look clean and inviting. Crafted with Multi-Needle Quilt 3 Layer Quilting, it is finished in White tones and made for lasting comfort.&lt;br&gt;
+Product Dimensions: 80"L X 60"W X 2"H&lt;br&gt;
+Size: Queen&lt;/p&gt;
+&lt;p&gt;Materials: Multi-Needle Quilt 3 Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr">
@@ -28229,13 +28229,13 @@
       </c>
       <c r="G206" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LUPINE 2" Bunkie Board is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Multi-Needle Quilt 3 Layer Quilting, it brings a reliable, comfortable feel with White tones.
-Product Dimensions: 75"L X 39"W X 2"H
-Size: Twin
-Materials: Multi-Needle Quilt 3 Layer Quilting.
-Color: White
-Weight: 22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LUPINE 2" Bunkie Board is built to support deeper, more restful sleep with a comfortable, balanced feel. Its Mattress design keeps the look clean and inviting. Built from Multi-Needle Quilt 3 Layer Quilting, it brings a reliable, comfortable feel with White tones.&lt;br&gt;
+Product Dimensions: 75"L X 39"W X 2"H&lt;br&gt;
+Size: Twin&lt;/p&gt;
+&lt;p&gt;Materials: Multi-Needle Quilt 3 Layer Quilting.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr">
@@ -28363,12 +28363,12 @@
       </c>
       <c r="G207" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Sleep easy with LUPINE 2" Bunkie Board, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.
-Product Dimensions: 80"L X 39"W X 2"H
-Size: Twin XL
-Color: White
-Weight: 22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Sleep easy with LUPINE 2" Bunkie Board, designed to deliver comfort and steady support night after night. Its Mattress design keeps the look clean and inviting. Finished in White tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80"L X 39"W X 2"H&lt;br&gt;
+Size: Twin XL&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr">

--- a/FOA Singles/Mattress-Single.xlsx
+++ b/FOA Singles/Mattress-Single.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD207"/>
+  <dimension ref="A1:AG207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="63" customWidth="1" min="7" max="7"/>
@@ -751,6 +751,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -886,7 +901,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Mattress, AFTON</t>
+          <t>Mattress, AFTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1052,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Mattress, AFTON</t>
+          <t>Mattress, AFTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1203,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Mattress, AFTON</t>
+          <t>Mattress, AFTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1354,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Mattress, AFTON</t>
+          <t>Mattress, AFTON, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1500,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Mattress, ALEKSA</t>
+          <t>Mattress, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1646,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Mattress, ALEKSA</t>
+          <t>Mattress, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1792,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Mattress, ALEKSA</t>
+          <t>Mattress, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1938,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Mattress, ALEKSA</t>
+          <t>Mattress, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -1955,7 +2090,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2242,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2394,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2546,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2695,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2847,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2999,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -2911,7 +3151,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3303,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3452,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3604,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3756,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3908,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3727,7 +4057,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -3864,7 +4209,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4361,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4513,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4665,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4817,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4958,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Mattress, ARTEMISIA</t>
+          <t>Mattress, ARTEMISIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4674,7 +5109,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Mattress, BIRD OF PARADISE</t>
+          <t>Mattress, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4810,7 +5260,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Mattress, BIRD OF PARADISE</t>
+          <t>Mattress, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -4946,7 +5411,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Mattress, BIRD OF PARADISE</t>
+          <t>Mattress, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5562,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Mattress, BIRD OF PARADISE</t>
+          <t>Mattress, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5713,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Mattress, BIRD OF PARADISE</t>
+          <t>Mattress, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5862,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Mattress, CATMINT</t>
+          <t>Mattress, CATMINT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5486,7 +6011,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Mattress, CATMINT</t>
+          <t>Mattress, CATMINT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5620,7 +6160,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Mattress, CATMINT</t>
+          <t>Mattress, CATMINT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5756,7 +6311,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Mattress, CATMINT</t>
+          <t>Mattress, CATMINT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -5892,7 +6462,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Mattress, CATMINT</t>
+          <t>Mattress, CATMINT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6613,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Mattress, CATMINT</t>
+          <t>Mattress, CATMINT, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6765,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6917,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6439,7 +7069,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6576,7 +7221,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6713,7 +7373,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6850,7 +7525,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -6987,7 +7677,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7829,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7981,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7398,7 +8133,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7535,7 +8285,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7672,7 +8437,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Mattress, COREOPSIS</t>
+          <t>Mattress, COREOPSIS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7806,7 +8586,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -7940,7 +8735,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8879,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8203,7 +9028,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8332,7 +9172,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8466,7 +9321,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8600,7 +9470,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Mattress, DAISY</t>
+          <t>Mattress, DAISY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8729,7 +9614,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Mattress, DERRY</t>
+          <t>Mattress, DERRY, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -8865,7 +9765,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9916,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9137,7 +10067,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9273,7 +10218,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9409,7 +10369,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9545,7 +10520,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9681,7 +10671,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9817,7 +10822,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -9953,7 +10973,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10089,7 +11124,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10225,7 +11275,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10361,7 +11426,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10497,7 +11577,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Mattress, EDELWEISS</t>
+          <t>Mattress, EDELWEISS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10633,7 +11728,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Mattress, EDREA</t>
+          <t>Mattress, EDREA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10769,7 +11879,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Mattress, EDREA</t>
+          <t>Mattress, EDREA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -10905,7 +12030,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Mattress, EDREA</t>
+          <t>Mattress, EDREA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11041,7 +12181,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Mattress, EDREA</t>
+          <t>Mattress, EDREA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11177,7 +12332,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Mattress, ELBERTYNA</t>
+          <t>Mattress, ELBERTYNA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11313,7 +12483,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Mattress, ELBERTYNA</t>
+          <t>Mattress, ELBERTYNA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11449,7 +12634,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Mattress, ELBERTYNA</t>
+          <t>Mattress, ELBERTYNA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11585,7 +12785,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Mattress, ELBERTYNA</t>
+          <t>Mattress, ELBERTYNA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11721,7 +12936,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Mattress, ELBERTYNA</t>
+          <t>Mattress, ELBERTYNA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11858,7 +13088,22 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -11995,7 +13240,22 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12132,7 +13392,22 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12269,7 +13544,22 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12406,7 +13696,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12543,7 +13848,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12680,7 +14000,22 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12817,7 +14152,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -12954,7 +14304,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13091,7 +14456,22 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13228,7 +14608,22 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13365,7 +14760,22 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Mattress, FORSYTHIA</t>
+          <t>Mattress, FORSYTHIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13501,7 +14911,22 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13637,7 +15062,22 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13773,7 +15213,22 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -13909,7 +15364,22 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14045,7 +15515,22 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14181,7 +15666,22 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14317,7 +15817,22 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14453,7 +15968,22 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Mattress, HOLLYHOCK</t>
+          <t>Mattress, HOLLYHOCK, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14589,7 +16119,22 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Mattress, JALEN</t>
+          <t>Mattress, JALEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14725,7 +16270,22 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Mattress, JALEN</t>
+          <t>Mattress, JALEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14861,7 +16421,22 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Mattress, JALEN</t>
+          <t>Mattress, JALEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -14997,7 +16572,22 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Mattress, JALEN</t>
+          <t>Mattress, JALEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15133,7 +16723,22 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Mattress, JALEN</t>
+          <t>Mattress, JALEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15269,7 +16874,22 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Mattress, LILIUM</t>
+          <t>Mattress, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15405,7 +17025,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Mattress, LILIUM</t>
+          <t>Mattress, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15541,7 +17176,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Mattress, LILIUM</t>
+          <t>Mattress, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15677,7 +17327,22 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Mattress, LILIUM</t>
+          <t>Mattress, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15813,7 +17478,22 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Mattress, LILIUM</t>
+          <t>Mattress, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -15939,7 +17619,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Mattress, MADDER</t>
+          <t>Mattress, MADDER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16071,7 +17766,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Mattress, MADDER</t>
+          <t>Mattress, MADDER, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16207,7 +17917,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16343,7 +18068,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16479,7 +18219,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16615,7 +18370,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16751,7 +18521,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -16887,7 +18672,22 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17023,7 +18823,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17159,7 +18974,22 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17295,7 +19125,22 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17431,7 +19276,22 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17567,7 +19427,22 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17703,7 +19578,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Mattress, NASTURTIUM</t>
+          <t>Mattress, NASTURTIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17839,7 +19729,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Mattress, SALVIA</t>
+          <t>Mattress, SALVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -17975,7 +19880,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Mattress, SALVIA</t>
+          <t>Mattress, SALVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18111,7 +20031,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Mattress, SALVIA</t>
+          <t>Mattress, SALVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18247,7 +20182,22 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Mattress, SALVIA</t>
+          <t>Mattress, SALVIA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18383,7 +20333,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Mattress, SIDDALEE</t>
+          <t>Mattress, SIDDALEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18519,7 +20484,22 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Mattress, SIDDALEE</t>
+          <t>Mattress, SIDDALEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18655,7 +20635,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Mattress, SIDDALEE</t>
+          <t>Mattress, SIDDALEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18791,7 +20786,22 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Mattress, SIDDALEE</t>
+          <t>Mattress, SIDDALEE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -18927,7 +20937,22 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Mattress, STORMIN</t>
+          <t>Mattress, STORMIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19063,7 +21088,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Mattress, STORMIN</t>
+          <t>Mattress, STORMIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19199,7 +21239,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Mattress, STORMIN</t>
+          <t>Mattress, STORMIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19335,7 +21390,22 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Mattress, STORMIN</t>
+          <t>Mattress, STORMIN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19473,7 +21543,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Mattress, VERBENA</t>
+          <t>Mattress, VERBENA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19611,7 +21696,22 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Mattress, VERBENA</t>
+          <t>Mattress, VERBENA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19749,7 +21849,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Mattress, VERBENA</t>
+          <t>Mattress, VERBENA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -19887,7 +22002,22 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Mattress, VERBENA</t>
+          <t>Mattress, VERBENA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattresses</t>
         </is>
       </c>
     </row>
@@ -20016,7 +22146,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, AKSEL</t>
+          <t>Mattress, Futon Mattress, AKSEL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20145,7 +22290,22 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, AKSEL</t>
+          <t>Mattress, Futon Mattress, AKSEL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20278,7 +22438,22 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, AKSEL</t>
+          <t>Mattress, Futon Mattress, AKSEL, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20404,7 +22579,22 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, KNOX</t>
+          <t>Mattress, Futon Mattress, KNOX, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20530,7 +22720,22 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, KNOX</t>
+          <t>Mattress, Futon Mattress, KNOX, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20656,7 +22861,22 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, KNOX</t>
+          <t>Mattress, Futon Mattress, KNOX, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20782,7 +23002,22 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, KNOX</t>
+          <t>Mattress, Futon Mattress, KNOX, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -20908,7 +23143,22 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, KNOX</t>
+          <t>Mattress, Futon Mattress, KNOX, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -21034,7 +23284,22 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Mattress, Futon Mattress, KNOX</t>
+          <t>Mattress, Futon Mattress, KNOX, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Futons &gt; Futon Pads</t>
         </is>
       </c>
     </row>
@@ -21163,7 +23428,22 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, ALEKSA</t>
+          <t>Mattress, Foundation, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -21292,7 +23572,22 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, ALEKSA</t>
+          <t>Mattress, Foundation, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -21421,7 +23716,22 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, ALEKSA</t>
+          <t>Mattress, Foundation, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -21550,7 +23860,22 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, ALEKSA</t>
+          <t>Mattress, Foundation, ALEKSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -21684,7 +24009,22 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, BIRD OF PARADISE</t>
+          <t>Mattress, Foundation, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -21818,7 +24158,22 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, BIRD OF PARADISE</t>
+          <t>Mattress, Foundation, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -21952,7 +24307,22 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, BIRD OF PARADISE</t>
+          <t>Mattress, Foundation, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22086,7 +24456,22 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, BIRD OF PARADISE</t>
+          <t>Mattress, Foundation, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22220,7 +24605,22 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, BIRD OF PARADISE</t>
+          <t>Mattress, Foundation, BIRD OF PARADISE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22354,7 +24754,22 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, LILIUM</t>
+          <t>Mattress, Foundation, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22488,7 +24903,22 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, LILIUM</t>
+          <t>Mattress, Foundation, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22622,7 +25052,22 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, LILIUM</t>
+          <t>Mattress, Foundation, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22756,7 +25201,22 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, LILIUM</t>
+          <t>Mattress, Foundation, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -22890,7 +25350,22 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>Mattress, Foundation, LILIUM</t>
+          <t>Mattress, Foundation, LILIUM, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations</t>
         </is>
       </c>
     </row>
@@ -23016,7 +25491,22 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23148,7 +25638,22 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23282,7 +25787,22 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23416,7 +25936,22 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23548,7 +26083,22 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23680,7 +26230,22 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23814,7 +26379,22 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -23948,7 +26528,22 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24082,7 +26677,22 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24216,7 +26826,22 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24350,7 +26975,22 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24484,7 +27124,22 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24618,7 +27273,22 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24744,7 +27414,22 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -24878,7 +27563,22 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25012,7 +27712,22 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25138,7 +27853,22 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25264,7 +27994,22 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25390,7 +28135,22 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25524,7 +28284,22 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25658,7 +28433,22 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25792,7 +28582,22 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, FRAMOS</t>
+          <t>Mattress, Bed Frame, FRAMOS, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -25920,7 +28725,22 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE I</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26054,7 +28874,22 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE I</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26188,7 +29023,22 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE I</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26322,7 +29172,22 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE I</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE I, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26450,7 +29315,22 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE II</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE II, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26584,7 +29464,22 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE II</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE II, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26718,7 +29613,22 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE II</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE II, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26852,7 +29762,22 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE II</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE II, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -26986,7 +29911,22 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE III</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27120,7 +30060,22 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE III</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27254,7 +30209,22 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE III</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27388,7 +30358,22 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE III</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27522,7 +30507,22 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE III</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27656,7 +30656,22 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Mattress, Bed Frame, SOMNERSIDE III</t>
+          <t>Mattress, Bed Frame, SOMNERSIDE III, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -27790,7 +30805,22 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>Mattress, Bunkie Board, LUPINE</t>
+          <t>Mattress, Bunkie Board, LUPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations &gt; Bunkie Boards</t>
         </is>
       </c>
     </row>
@@ -27924,7 +30954,22 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>Mattress, Bunkie Board, LUPINE</t>
+          <t>Mattress, Bunkie Board, LUPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations &gt; Bunkie Boards</t>
         </is>
       </c>
     </row>
@@ -28058,7 +31103,22 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>Mattress, Bunkie Board, LUPINE</t>
+          <t>Mattress, Bunkie Board, LUPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations &gt; Bunkie Boards</t>
         </is>
       </c>
     </row>
@@ -28192,7 +31252,22 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>Mattress, Bunkie Board, LUPINE</t>
+          <t>Mattress, Bunkie Board, LUPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations &gt; Bunkie Boards</t>
         </is>
       </c>
     </row>
@@ -28326,7 +31401,22 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>Mattress, Bunkie Board, LUPINE</t>
+          <t>Mattress, Bunkie Board, LUPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations &gt; Bunkie Boards</t>
         </is>
       </c>
     </row>
@@ -28455,7 +31545,22 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>Mattress, Bunkie Board, LUPINE</t>
+          <t>Mattress, Bunkie Board, LUPINE, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Mattress Foundations &gt; Bunkie Boards</t>
         </is>
       </c>
     </row>
